--- a/relevamiento/plantilla_relevamiento_arboretum.xlsx
+++ b/relevamiento/plantilla_relevamiento_arboretum.xlsx
@@ -18,8 +18,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="10">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.000000"/>
+  </numFmts>
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +74,16 @@
       <b val="1"/>
       <color rgb="00B06A00"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E4A38"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="001E4A38"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="7">
@@ -133,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -153,6 +165,26 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -518,110 +550,124 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A17"/>
+  <dimension ref="A1:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>Relevamiento del Arboretum — Planilla de campo</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="14" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Cómo usar esta planilla</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>• Las columnas grises (ID, nombre científico, común, familia) YA vienen cargadas: son la referencia. NO las modifiques.</t>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>• Las columnas gris claro YA vienen cargadas como referencia: ID, nombre científico, común y familia; y también la latitud/longitud y el año de plantación de los árboles que ya estaban ubicados. NO hace falta re-medir esos datos.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>• Completá solo las columnas amarillas, fila por fila, para cada árbol identificado por su ID.</t>
+      <c r="A5" s="14" t="inlineStr">
+        <is>
+          <t>• Completá las columnas amarillas, fila por fila, para cada árbol identificado por su ID.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="A6" s="14" t="inlineStr">
+        <is>
+          <t>• Hay 9 árboles SIN coordenadas: sus celdas de latitud/longitud están en amarillo. Ubicarlos es la prioridad número 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="inlineStr">
+        <is>
+          <t>• Si notás un error en una coordenada ya cargada (gris), podés corregirla; si no, dejala como está.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="inlineStr">
         <is>
           <t>• La fila 2 es un EJEMPLO con el formato esperado: borrala antes de empezar a cargar.</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>• Los campos con lista desplegable (estado sanitario, nativo/exótico, caduco/perenne) se eligen del menú.</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="14" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
         <is>
           <t>Cómo medir</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="14" t="inlineStr">
         <is>
           <t>• DAP (diámetro): medí el tronco a 1,30 m del suelo. Si tenés cinta métrica común, medí el perímetro y dividilo por 3,1416.</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="14" t="inlineStr">
         <is>
           <t>• Altura: estimación en metros (podés usar apps de altura o referencia visual).</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>• Coordenadas: paradas junto al árbol, copiá lat/long del GPS del celular (6 decimales).</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr"/>
-    </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="16" t="inlineStr">
+        <is>
+          <t>• Coordenadas: parado junto al árbol, copiá lat/long del GPS del celular (6 decimales).</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="inlineStr">
         <is>
           <t>Prioridad (si el tiempo es corto, cargá primero esto)</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>1) Coordenadas de los árboles sin ubicar   2) estado sanitario   3) altura y diámetro   4) floración/fructificación   5) el resto.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="17" t="inlineStr">
+        <is>
+          <t>1) Coordenadas de los 9 árboles sin ubicar (celdas amarillas)   2) estado sanitario   3) altura y diámetro   4) floración/fructificación   5) el resto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Importante: el ID es la clave. Mientras el ID sea correcto, los datos se integran solos a la base del sitio.</t>
         </is>
@@ -872,8 +918,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E3" s="9" t="inlineStr"/>
-      <c r="F3" s="9" t="inlineStr"/>
+      <c r="E3" s="19" t="n">
+        <v>-38.056791</v>
+      </c>
+      <c r="F3" s="19" t="n">
+        <v>-57.680154</v>
+      </c>
       <c r="G3" s="9" t="inlineStr"/>
       <c r="H3" s="9" t="inlineStr"/>
       <c r="I3" s="9" t="inlineStr"/>
@@ -882,7 +932,9 @@
       <c r="L3" s="9" t="inlineStr"/>
       <c r="M3" s="9" t="inlineStr"/>
       <c r="N3" s="9" t="inlineStr"/>
-      <c r="O3" s="9" t="inlineStr"/>
+      <c r="O3" s="20" t="n">
+        <v>2004</v>
+      </c>
       <c r="P3" s="9" t="inlineStr"/>
       <c r="Q3" s="9" t="inlineStr"/>
       <c r="R3" s="9" t="inlineStr"/>
@@ -909,8 +961,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E4" s="10" t="inlineStr"/>
-      <c r="F4" s="10" t="inlineStr"/>
+      <c r="E4" s="19" t="n">
+        <v>-38.056472</v>
+      </c>
+      <c r="F4" s="19" t="n">
+        <v>-57.680521</v>
+      </c>
       <c r="G4" s="10" t="inlineStr"/>
       <c r="H4" s="10" t="inlineStr"/>
       <c r="I4" s="10" t="inlineStr"/>
@@ -946,8 +1002,12 @@
           <t>Fagaceae</t>
         </is>
       </c>
-      <c r="E5" s="9" t="inlineStr"/>
-      <c r="F5" s="9" t="inlineStr"/>
+      <c r="E5" s="19" t="n">
+        <v>-38.056541</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>-57.680555</v>
+      </c>
       <c r="G5" s="9" t="inlineStr"/>
       <c r="H5" s="9" t="inlineStr"/>
       <c r="I5" s="9" t="inlineStr"/>
@@ -979,8 +1039,12 @@
         </is>
       </c>
       <c r="D6" s="8" t="inlineStr"/>
-      <c r="E6" s="10" t="inlineStr"/>
-      <c r="F6" s="10" t="inlineStr"/>
+      <c r="E6" s="19" t="n">
+        <v>-38.056569</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>-57.680685</v>
+      </c>
       <c r="G6" s="10" t="inlineStr"/>
       <c r="H6" s="10" t="inlineStr"/>
       <c r="I6" s="10" t="inlineStr"/>
@@ -1016,8 +1080,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr"/>
-      <c r="F7" s="9" t="inlineStr"/>
+      <c r="E7" s="19" t="n">
+        <v>-38.056549</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>-57.680737</v>
+      </c>
       <c r="G7" s="9" t="inlineStr"/>
       <c r="H7" s="9" t="inlineStr"/>
       <c r="I7" s="9" t="inlineStr"/>
@@ -1053,8 +1121,12 @@
           <t>Casuarinaceae</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr"/>
-      <c r="F8" s="10" t="inlineStr"/>
+      <c r="E8" s="19" t="n">
+        <v>-38.056437</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>-57.680856</v>
+      </c>
       <c r="G8" s="10" t="inlineStr"/>
       <c r="H8" s="10" t="inlineStr"/>
       <c r="I8" s="10" t="inlineStr"/>
@@ -1090,8 +1162,12 @@
           <t>Apocynaceae</t>
         </is>
       </c>
-      <c r="E9" s="9" t="inlineStr"/>
-      <c r="F9" s="9" t="inlineStr"/>
+      <c r="E9" s="19" t="n">
+        <v>-38.056372</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>-57.681121</v>
+      </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
       <c r="I9" s="9" t="inlineStr"/>
@@ -1127,8 +1203,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr"/>
-      <c r="F10" s="10" t="inlineStr"/>
+      <c r="E10" s="19" t="n">
+        <v>-38.056239</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>-57.68099</v>
+      </c>
       <c r="G10" s="10" t="inlineStr"/>
       <c r="H10" s="10" t="inlineStr"/>
       <c r="I10" s="10" t="inlineStr"/>
@@ -1164,8 +1244,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E11" s="9" t="inlineStr"/>
-      <c r="F11" s="9" t="inlineStr"/>
+      <c r="E11" s="19" t="n">
+        <v>-38.056201</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>-57.680907</v>
+      </c>
       <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
       <c r="I11" s="9" t="inlineStr"/>
@@ -1201,8 +1285,12 @@
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr"/>
-      <c r="F12" s="10" t="inlineStr"/>
+      <c r="E12" s="19" t="n">
+        <v>-38.056054</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>-57.680894</v>
+      </c>
       <c r="G12" s="10" t="inlineStr"/>
       <c r="H12" s="10" t="inlineStr"/>
       <c r="I12" s="10" t="inlineStr"/>
@@ -1234,8 +1322,12 @@
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="E13" s="9" t="inlineStr"/>
-      <c r="F13" s="9" t="inlineStr"/>
+      <c r="E13" s="19" t="n">
+        <v>-38.056331</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-57.680572</v>
+      </c>
       <c r="G13" s="9" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr"/>
       <c r="I13" s="9" t="inlineStr"/>
@@ -1271,8 +1363,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr"/>
-      <c r="F14" s="10" t="inlineStr"/>
+      <c r="E14" s="19" t="n">
+        <v>-38.056329</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>-57.68043</v>
+      </c>
       <c r="G14" s="10" t="inlineStr"/>
       <c r="H14" s="10" t="inlineStr"/>
       <c r="I14" s="10" t="inlineStr"/>
@@ -1308,8 +1404,12 @@
           <t>Fagaceae</t>
         </is>
       </c>
-      <c r="E15" s="9" t="inlineStr"/>
-      <c r="F15" s="9" t="inlineStr"/>
+      <c r="E15" s="19" t="n">
+        <v>-38.056373</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>-57.679866</v>
+      </c>
       <c r="G15" s="9" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
       <c r="I15" s="9" t="inlineStr"/>
@@ -1345,8 +1445,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr"/>
-      <c r="F16" s="10" t="inlineStr"/>
+      <c r="E16" s="19" t="n">
+        <v>-38.056551</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>-57.679765</v>
+      </c>
       <c r="G16" s="10" t="inlineStr"/>
       <c r="H16" s="10" t="inlineStr"/>
       <c r="I16" s="10" t="inlineStr"/>
@@ -1378,8 +1482,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="9" t="inlineStr"/>
+      <c r="E17" s="19" t="n">
+        <v>-38.056644</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>-57.679769</v>
+      </c>
       <c r="G17" s="9" t="inlineStr"/>
       <c r="H17" s="9" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr"/>
@@ -1415,8 +1523,12 @@
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr"/>
-      <c r="F18" s="10" t="inlineStr"/>
+      <c r="E18" s="19" t="n">
+        <v>-38.056727</v>
+      </c>
+      <c r="F18" s="19" t="n">
+        <v>-57.679967</v>
+      </c>
       <c r="G18" s="10" t="inlineStr"/>
       <c r="H18" s="10" t="inlineStr"/>
       <c r="I18" s="10" t="inlineStr"/>
@@ -1425,7 +1537,9 @@
       <c r="L18" s="10" t="inlineStr"/>
       <c r="M18" s="10" t="inlineStr"/>
       <c r="N18" s="10" t="inlineStr"/>
-      <c r="O18" s="10" t="inlineStr"/>
+      <c r="O18" s="20" t="n">
+        <v>1988</v>
+      </c>
       <c r="P18" s="10" t="inlineStr"/>
       <c r="Q18" s="10" t="inlineStr"/>
       <c r="R18" s="10" t="inlineStr"/>
@@ -1452,8 +1566,12 @@
           <t>Caprifoliaceae</t>
         </is>
       </c>
-      <c r="E19" s="9" t="inlineStr"/>
-      <c r="F19" s="9" t="inlineStr"/>
+      <c r="E19" s="19" t="n">
+        <v>-38.056678</v>
+      </c>
+      <c r="F19" s="19" t="n">
+        <v>-57.6801</v>
+      </c>
       <c r="G19" s="9" t="inlineStr"/>
       <c r="H19" s="9" t="inlineStr"/>
       <c r="I19" s="9" t="inlineStr"/>
@@ -1489,8 +1607,12 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr"/>
-      <c r="F20" s="10" t="inlineStr"/>
+      <c r="E20" s="19" t="n">
+        <v>-38.056844</v>
+      </c>
+      <c r="F20" s="19" t="n">
+        <v>-57.680508</v>
+      </c>
       <c r="G20" s="10" t="inlineStr"/>
       <c r="H20" s="10" t="inlineStr"/>
       <c r="I20" s="10" t="inlineStr"/>
@@ -1526,8 +1648,12 @@
           <t>Magnoliaceae</t>
         </is>
       </c>
-      <c r="E21" s="9" t="inlineStr"/>
-      <c r="F21" s="9" t="inlineStr"/>
+      <c r="E21" s="19" t="n">
+        <v>-38.057062</v>
+      </c>
+      <c r="F21" s="19" t="n">
+        <v>-57.680232</v>
+      </c>
       <c r="G21" s="9" t="inlineStr"/>
       <c r="H21" s="9" t="inlineStr"/>
       <c r="I21" s="9" t="inlineStr"/>
@@ -1563,8 +1689,12 @@
           <t>Platanaceae</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr"/>
-      <c r="F22" s="10" t="inlineStr"/>
+      <c r="E22" s="19" t="n">
+        <v>-38.057076</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>-57.680527</v>
+      </c>
       <c r="G22" s="10" t="inlineStr"/>
       <c r="H22" s="10" t="inlineStr"/>
       <c r="I22" s="10" t="inlineStr"/>
@@ -1600,8 +1730,12 @@
           <t>Malvaceae</t>
         </is>
       </c>
-      <c r="E23" s="9" t="inlineStr"/>
-      <c r="F23" s="9" t="inlineStr"/>
+      <c r="E23" s="19" t="n">
+        <v>-38.057192</v>
+      </c>
+      <c r="F23" s="19" t="n">
+        <v>-57.680583</v>
+      </c>
       <c r="G23" s="9" t="inlineStr"/>
       <c r="H23" s="9" t="inlineStr"/>
       <c r="I23" s="9" t="inlineStr"/>
@@ -1610,7 +1744,9 @@
       <c r="L23" s="9" t="inlineStr"/>
       <c r="M23" s="9" t="inlineStr"/>
       <c r="N23" s="9" t="inlineStr"/>
-      <c r="O23" s="9" t="inlineStr"/>
+      <c r="O23" s="20" t="n">
+        <v>1990</v>
+      </c>
       <c r="P23" s="9" t="inlineStr"/>
       <c r="Q23" s="9" t="inlineStr"/>
       <c r="R23" s="9" t="inlineStr"/>
@@ -1637,8 +1773,12 @@
           <t>Araucariaceae</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr"/>
-      <c r="F24" s="10" t="inlineStr"/>
+      <c r="E24" s="19" t="n">
+        <v>-38.056909</v>
+      </c>
+      <c r="F24" s="19" t="n">
+        <v>-57.680885</v>
+      </c>
       <c r="G24" s="10" t="inlineStr"/>
       <c r="H24" s="10" t="inlineStr"/>
       <c r="I24" s="10" t="inlineStr"/>
@@ -1674,8 +1814,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="9" t="inlineStr"/>
+      <c r="E25" s="19" t="n">
+        <v>-38.05684</v>
+      </c>
+      <c r="F25" s="19" t="n">
+        <v>-57.681064</v>
+      </c>
       <c r="G25" s="9" t="inlineStr"/>
       <c r="H25" s="9" t="inlineStr"/>
       <c r="I25" s="9" t="inlineStr"/>
@@ -1711,8 +1855,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr"/>
-      <c r="F26" s="10" t="inlineStr"/>
+      <c r="E26" s="19" t="n">
+        <v>-38.056934</v>
+      </c>
+      <c r="F26" s="19" t="n">
+        <v>-57.681113</v>
+      </c>
       <c r="G26" s="10" t="inlineStr"/>
       <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="10" t="inlineStr"/>
@@ -1748,8 +1896,12 @@
           <t>Casuarinaceae</t>
         </is>
       </c>
-      <c r="E27" s="9" t="inlineStr"/>
-      <c r="F27" s="9" t="inlineStr"/>
+      <c r="E27" s="19" t="n">
+        <v>-38.056656</v>
+      </c>
+      <c r="F27" s="19" t="n">
+        <v>-57.68126</v>
+      </c>
       <c r="G27" s="9" t="inlineStr"/>
       <c r="H27" s="9" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr"/>
@@ -1785,8 +1937,12 @@
           <t>Fagaceae</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr"/>
-      <c r="F28" s="10" t="inlineStr"/>
+      <c r="E28" s="19" t="n">
+        <v>-38.055929</v>
+      </c>
+      <c r="F28" s="19" t="n">
+        <v>-57.680409</v>
+      </c>
       <c r="G28" s="10" t="inlineStr"/>
       <c r="H28" s="10" t="inlineStr"/>
       <c r="I28" s="10" t="inlineStr"/>
@@ -1822,8 +1978,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E29" s="9" t="inlineStr"/>
-      <c r="F29" s="9" t="inlineStr"/>
+      <c r="E29" s="19" t="n">
+        <v>-38.056056</v>
+      </c>
+      <c r="F29" s="19" t="n">
+        <v>-57.679651</v>
+      </c>
       <c r="G29" s="9" t="inlineStr"/>
       <c r="H29" s="9" t="inlineStr"/>
       <c r="I29" s="9" t="inlineStr"/>
@@ -1859,8 +2019,12 @@
           <t>Araucariaceae</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr"/>
-      <c r="F30" s="10" t="inlineStr"/>
+      <c r="E30" s="19" t="n">
+        <v>-38.056057</v>
+      </c>
+      <c r="F30" s="19" t="n">
+        <v>-57.679449</v>
+      </c>
       <c r="G30" s="10" t="inlineStr"/>
       <c r="H30" s="10" t="inlineStr"/>
       <c r="I30" s="10" t="inlineStr"/>
@@ -1896,8 +2060,12 @@
           <t>Salicaceae</t>
         </is>
       </c>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="9" t="inlineStr"/>
+      <c r="E31" s="19" t="n">
+        <v>-38.056168</v>
+      </c>
+      <c r="F31" s="19" t="n">
+        <v>-57.679357</v>
+      </c>
       <c r="G31" s="9" t="inlineStr"/>
       <c r="H31" s="9" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr"/>
@@ -1933,8 +2101,12 @@
           <t>Sapindaceae</t>
         </is>
       </c>
-      <c r="E32" s="10" t="inlineStr"/>
-      <c r="F32" s="10" t="inlineStr"/>
+      <c r="E32" s="19" t="n">
+        <v>-38.056127</v>
+      </c>
+      <c r="F32" s="19" t="n">
+        <v>-57.679297</v>
+      </c>
       <c r="G32" s="10" t="inlineStr"/>
       <c r="H32" s="10" t="inlineStr"/>
       <c r="I32" s="10" t="inlineStr"/>
@@ -1970,8 +2142,12 @@
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="E33" s="9" t="inlineStr"/>
-      <c r="F33" s="9" t="inlineStr"/>
+      <c r="E33" s="19" t="n">
+        <v>-38.056093</v>
+      </c>
+      <c r="F33" s="19" t="n">
+        <v>-57.679557</v>
+      </c>
       <c r="G33" s="9" t="inlineStr"/>
       <c r="H33" s="9" t="inlineStr"/>
       <c r="I33" s="9" t="inlineStr"/>
@@ -2007,8 +2183,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E34" s="10" t="inlineStr"/>
-      <c r="F34" s="10" t="inlineStr"/>
+      <c r="E34" s="19" t="n">
+        <v>-38.056374</v>
+      </c>
+      <c r="F34" s="19" t="n">
+        <v>-57.679314</v>
+      </c>
       <c r="G34" s="10" t="inlineStr"/>
       <c r="H34" s="10" t="inlineStr"/>
       <c r="I34" s="10" t="inlineStr"/>
@@ -2044,8 +2224,12 @@
           <t>Altingiaceae</t>
         </is>
       </c>
-      <c r="E35" s="9" t="inlineStr"/>
-      <c r="F35" s="9" t="inlineStr"/>
+      <c r="E35" s="19" t="n">
+        <v>-38.056545</v>
+      </c>
+      <c r="F35" s="19" t="n">
+        <v>-57.679395</v>
+      </c>
       <c r="G35" s="9" t="inlineStr"/>
       <c r="H35" s="9" t="inlineStr"/>
       <c r="I35" s="9" t="inlineStr"/>
@@ -2081,8 +2265,8 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E36" s="10" t="inlineStr"/>
-      <c r="F36" s="10" t="inlineStr"/>
+      <c r="E36" s="9" t="inlineStr"/>
+      <c r="F36" s="9" t="inlineStr"/>
       <c r="G36" s="10" t="inlineStr"/>
       <c r="H36" s="10" t="inlineStr"/>
       <c r="I36" s="10" t="inlineStr"/>
@@ -2155,8 +2339,8 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E38" s="10" t="inlineStr"/>
-      <c r="F38" s="10" t="inlineStr"/>
+      <c r="E38" s="9" t="inlineStr"/>
+      <c r="F38" s="9" t="inlineStr"/>
       <c r="G38" s="10" t="inlineStr"/>
       <c r="H38" s="10" t="inlineStr"/>
       <c r="I38" s="10" t="inlineStr"/>
@@ -2229,8 +2413,8 @@
           <t>Rhamnaceae</t>
         </is>
       </c>
-      <c r="E40" s="10" t="inlineStr"/>
-      <c r="F40" s="10" t="inlineStr"/>
+      <c r="E40" s="9" t="inlineStr"/>
+      <c r="F40" s="9" t="inlineStr"/>
       <c r="G40" s="10" t="inlineStr"/>
       <c r="H40" s="10" t="inlineStr"/>
       <c r="I40" s="10" t="inlineStr"/>
@@ -2303,8 +2487,8 @@
           <t>Cannabaceae</t>
         </is>
       </c>
-      <c r="E42" s="10" t="inlineStr"/>
-      <c r="F42" s="10" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="9" t="inlineStr"/>
       <c r="G42" s="10" t="inlineStr"/>
       <c r="H42" s="10" t="inlineStr"/>
       <c r="I42" s="10" t="inlineStr"/>
@@ -2377,8 +2561,8 @@
           <t>Magnoliaceae</t>
         </is>
       </c>
-      <c r="E44" s="10" t="inlineStr"/>
-      <c r="F44" s="10" t="inlineStr"/>
+      <c r="E44" s="9" t="inlineStr"/>
+      <c r="F44" s="9" t="inlineStr"/>
       <c r="G44" s="10" t="inlineStr"/>
       <c r="H44" s="10" t="inlineStr"/>
       <c r="I44" s="10" t="inlineStr"/>
@@ -2414,8 +2598,12 @@
           <t>Fagaceae</t>
         </is>
       </c>
-      <c r="E45" s="9" t="inlineStr"/>
-      <c r="F45" s="9" t="inlineStr"/>
+      <c r="E45" s="19" t="n">
+        <v>-38.0558</v>
+      </c>
+      <c r="F45" s="19" t="n">
+        <v>-57.682849</v>
+      </c>
       <c r="G45" s="9" t="inlineStr"/>
       <c r="H45" s="9" t="inlineStr"/>
       <c r="I45" s="9" t="inlineStr"/>
@@ -2451,8 +2639,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E46" s="10" t="inlineStr"/>
-      <c r="F46" s="10" t="inlineStr"/>
+      <c r="E46" s="19" t="n">
+        <v>-38.05574</v>
+      </c>
+      <c r="F46" s="19" t="n">
+        <v>-57.682864</v>
+      </c>
       <c r="G46" s="10" t="inlineStr"/>
       <c r="H46" s="10" t="inlineStr"/>
       <c r="I46" s="10" t="inlineStr"/>
@@ -2488,8 +2680,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E47" s="9" t="inlineStr"/>
-      <c r="F47" s="9" t="inlineStr"/>
+      <c r="E47" s="19" t="n">
+        <v>-38.05573</v>
+      </c>
+      <c r="F47" s="19" t="n">
+        <v>-57.682739</v>
+      </c>
       <c r="G47" s="9" t="inlineStr"/>
       <c r="H47" s="9" t="inlineStr"/>
       <c r="I47" s="9" t="inlineStr"/>
@@ -2525,8 +2721,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E48" s="10" t="inlineStr"/>
-      <c r="F48" s="10" t="inlineStr"/>
+      <c r="E48" s="19" t="n">
+        <v>-38.05576</v>
+      </c>
+      <c r="F48" s="19" t="n">
+        <v>-57.682726</v>
+      </c>
       <c r="G48" s="10" t="inlineStr"/>
       <c r="H48" s="10" t="inlineStr"/>
       <c r="I48" s="10" t="inlineStr"/>
@@ -2562,8 +2762,12 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="E49" s="9" t="inlineStr"/>
-      <c r="F49" s="9" t="inlineStr"/>
+      <c r="E49" s="19" t="n">
+        <v>-38.05564</v>
+      </c>
+      <c r="F49" s="19" t="n">
+        <v>-57.682655</v>
+      </c>
       <c r="G49" s="9" t="inlineStr"/>
       <c r="H49" s="9" t="inlineStr"/>
       <c r="I49" s="9" t="inlineStr"/>
@@ -2599,8 +2803,12 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="E50" s="10" t="inlineStr"/>
-      <c r="F50" s="10" t="inlineStr"/>
+      <c r="E50" s="19" t="n">
+        <v>-38.05563</v>
+      </c>
+      <c r="F50" s="19" t="n">
+        <v>-57.682537</v>
+      </c>
       <c r="G50" s="10" t="inlineStr"/>
       <c r="H50" s="10" t="inlineStr"/>
       <c r="I50" s="10" t="inlineStr"/>
@@ -2632,8 +2840,12 @@
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr"/>
-      <c r="E51" s="9" t="inlineStr"/>
-      <c r="F51" s="9" t="inlineStr"/>
+      <c r="E51" s="19" t="n">
+        <v>-38.05561</v>
+      </c>
+      <c r="F51" s="19" t="n">
+        <v>-57.682472</v>
+      </c>
       <c r="G51" s="9" t="inlineStr"/>
       <c r="H51" s="9" t="inlineStr"/>
       <c r="I51" s="9" t="inlineStr"/>
@@ -2669,8 +2881,12 @@
           <t>Sapindaceae</t>
         </is>
       </c>
-      <c r="E52" s="10" t="inlineStr"/>
-      <c r="F52" s="10" t="inlineStr"/>
+      <c r="E52" s="19" t="n">
+        <v>-38.05576</v>
+      </c>
+      <c r="F52" s="19" t="n">
+        <v>-57.682429</v>
+      </c>
       <c r="G52" s="10" t="inlineStr"/>
       <c r="H52" s="10" t="inlineStr"/>
       <c r="I52" s="10" t="inlineStr"/>
@@ -2679,7 +2895,9 @@
       <c r="L52" s="10" t="inlineStr"/>
       <c r="M52" s="10" t="inlineStr"/>
       <c r="N52" s="10" t="inlineStr"/>
-      <c r="O52" s="10" t="inlineStr"/>
+      <c r="O52" s="20" t="n">
+        <v>2002</v>
+      </c>
       <c r="P52" s="10" t="inlineStr"/>
       <c r="Q52" s="10" t="inlineStr"/>
       <c r="R52" s="10" t="inlineStr"/>
@@ -2706,8 +2924,12 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="E53" s="9" t="inlineStr"/>
-      <c r="F53" s="9" t="inlineStr"/>
+      <c r="E53" s="19" t="n">
+        <v>-38.05573</v>
+      </c>
+      <c r="F53" s="19" t="n">
+        <v>-57.682438</v>
+      </c>
       <c r="G53" s="9" t="inlineStr"/>
       <c r="H53" s="9" t="inlineStr"/>
       <c r="I53" s="9" t="inlineStr"/>
@@ -2743,8 +2965,12 @@
           <t>Sapindaceae</t>
         </is>
       </c>
-      <c r="E54" s="10" t="inlineStr"/>
-      <c r="F54" s="10" t="inlineStr"/>
+      <c r="E54" s="19" t="n">
+        <v>-38.05572</v>
+      </c>
+      <c r="F54" s="19" t="n">
+        <v>-57.682395</v>
+      </c>
       <c r="G54" s="10" t="inlineStr"/>
       <c r="H54" s="10" t="inlineStr"/>
       <c r="I54" s="10" t="inlineStr"/>
@@ -2780,8 +3006,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E55" s="9" t="inlineStr"/>
-      <c r="F55" s="9" t="inlineStr"/>
+      <c r="E55" s="19" t="n">
+        <v>-38.05574</v>
+      </c>
+      <c r="F55" s="19" t="n">
+        <v>-57.68213</v>
+      </c>
       <c r="G55" s="9" t="inlineStr"/>
       <c r="H55" s="9" t="inlineStr"/>
       <c r="I55" s="9" t="inlineStr"/>
@@ -2817,8 +3047,12 @@
           <t>Olives</t>
         </is>
       </c>
-      <c r="E56" s="10" t="inlineStr"/>
-      <c r="F56" s="10" t="inlineStr"/>
+      <c r="E56" s="19" t="n">
+        <v>-38.05569</v>
+      </c>
+      <c r="F56" s="19" t="n">
+        <v>-57.68208</v>
+      </c>
       <c r="G56" s="10" t="inlineStr"/>
       <c r="H56" s="10" t="inlineStr"/>
       <c r="I56" s="10" t="inlineStr"/>
@@ -2850,8 +3084,12 @@
         </is>
       </c>
       <c r="D57" s="8" t="inlineStr"/>
-      <c r="E57" s="9" t="inlineStr"/>
-      <c r="F57" s="9" t="inlineStr"/>
+      <c r="E57" s="19" t="n">
+        <v>-38.05572</v>
+      </c>
+      <c r="F57" s="19" t="n">
+        <v>-57.68198</v>
+      </c>
       <c r="G57" s="9" t="inlineStr"/>
       <c r="H57" s="9" t="inlineStr"/>
       <c r="I57" s="9" t="inlineStr"/>
@@ -2887,8 +3125,12 @@
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="E58" s="10" t="inlineStr"/>
-      <c r="F58" s="10" t="inlineStr"/>
+      <c r="E58" s="19" t="n">
+        <v>-38.05585</v>
+      </c>
+      <c r="F58" s="19" t="n">
+        <v>-57.681933</v>
+      </c>
       <c r="G58" s="10" t="inlineStr"/>
       <c r="H58" s="10" t="inlineStr"/>
       <c r="I58" s="10" t="inlineStr"/>
@@ -2920,8 +3162,12 @@
         </is>
       </c>
       <c r="D59" s="8" t="inlineStr"/>
-      <c r="E59" s="9" t="inlineStr"/>
-      <c r="F59" s="9" t="inlineStr"/>
+      <c r="E59" s="19" t="n">
+        <v>-38.05578</v>
+      </c>
+      <c r="F59" s="19" t="n">
+        <v>-57.68175</v>
+      </c>
       <c r="G59" s="9" t="inlineStr"/>
       <c r="H59" s="9" t="inlineStr"/>
       <c r="I59" s="9" t="inlineStr"/>
@@ -2957,8 +3203,12 @@
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="E60" s="10" t="inlineStr"/>
-      <c r="F60" s="10" t="inlineStr"/>
+      <c r="E60" s="19" t="n">
+        <v>-38.0559</v>
+      </c>
+      <c r="F60" s="19" t="n">
+        <v>-57.681743</v>
+      </c>
       <c r="G60" s="10" t="inlineStr"/>
       <c r="H60" s="10" t="inlineStr"/>
       <c r="I60" s="10" t="inlineStr"/>
@@ -2994,8 +3244,12 @@
           <t>Fagaceae</t>
         </is>
       </c>
-      <c r="E61" s="9" t="inlineStr"/>
-      <c r="F61" s="9" t="inlineStr"/>
+      <c r="E61" s="19" t="n">
+        <v>-38.05577</v>
+      </c>
+      <c r="F61" s="19" t="n">
+        <v>-57.681628</v>
+      </c>
       <c r="G61" s="9" t="inlineStr"/>
       <c r="H61" s="9" t="inlineStr"/>
       <c r="I61" s="9" t="inlineStr"/>
@@ -3031,8 +3285,12 @@
           <t>Sapindaceae</t>
         </is>
       </c>
-      <c r="E62" s="10" t="inlineStr"/>
-      <c r="F62" s="10" t="inlineStr"/>
+      <c r="E62" s="19" t="n">
+        <v>-38.05564</v>
+      </c>
+      <c r="F62" s="19" t="n">
+        <v>-57.681649</v>
+      </c>
       <c r="G62" s="10" t="inlineStr"/>
       <c r="H62" s="10" t="inlineStr"/>
       <c r="I62" s="10" t="inlineStr"/>
@@ -3068,8 +3326,12 @@
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="E63" s="9" t="inlineStr"/>
-      <c r="F63" s="9" t="inlineStr"/>
+      <c r="E63" s="19" t="n">
+        <v>-38.05567</v>
+      </c>
+      <c r="F63" s="19" t="n">
+        <v>-57.681577</v>
+      </c>
       <c r="G63" s="9" t="inlineStr"/>
       <c r="H63" s="9" t="inlineStr"/>
       <c r="I63" s="9" t="inlineStr"/>
@@ -3105,8 +3367,12 @@
           <t>Altingiaceae</t>
         </is>
       </c>
-      <c r="E64" s="10" t="inlineStr"/>
-      <c r="F64" s="10" t="inlineStr"/>
+      <c r="E64" s="19" t="n">
+        <v>-38.05553</v>
+      </c>
+      <c r="F64" s="19" t="n">
+        <v>-57.681601</v>
+      </c>
       <c r="G64" s="10" t="inlineStr"/>
       <c r="H64" s="10" t="inlineStr"/>
       <c r="I64" s="10" t="inlineStr"/>
@@ -3142,8 +3408,12 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="E65" s="9" t="inlineStr"/>
-      <c r="F65" s="9" t="inlineStr"/>
+      <c r="E65" s="19" t="n">
+        <v>-38.05554</v>
+      </c>
+      <c r="F65" s="19" t="n">
+        <v>-57.681418</v>
+      </c>
       <c r="G65" s="9" t="inlineStr"/>
       <c r="H65" s="9" t="inlineStr"/>
       <c r="I65" s="9" t="inlineStr"/>
@@ -3175,8 +3445,12 @@
         </is>
       </c>
       <c r="D66" s="8" t="inlineStr"/>
-      <c r="E66" s="10" t="inlineStr"/>
-      <c r="F66" s="10" t="inlineStr"/>
+      <c r="E66" s="19" t="n">
+        <v>-38.0555</v>
+      </c>
+      <c r="F66" s="19" t="n">
+        <v>-57.681415</v>
+      </c>
       <c r="G66" s="10" t="inlineStr"/>
       <c r="H66" s="10" t="inlineStr"/>
       <c r="I66" s="10" t="inlineStr"/>
@@ -3212,8 +3486,12 @@
           <t>Rosaceae</t>
         </is>
       </c>
-      <c r="E67" s="9" t="inlineStr"/>
-      <c r="F67" s="9" t="inlineStr"/>
+      <c r="E67" s="19" t="n">
+        <v>-38.0556</v>
+      </c>
+      <c r="F67" s="19" t="n">
+        <v>-57.681349</v>
+      </c>
       <c r="G67" s="9" t="inlineStr"/>
       <c r="H67" s="9" t="inlineStr"/>
       <c r="I67" s="9" t="inlineStr"/>
@@ -3249,8 +3527,12 @@
           <t>Sapindaceae</t>
         </is>
       </c>
-      <c r="E68" s="10" t="inlineStr"/>
-      <c r="F68" s="10" t="inlineStr"/>
+      <c r="E68" s="19" t="n">
+        <v>-38.05523</v>
+      </c>
+      <c r="F68" s="19" t="n">
+        <v>-57.681177</v>
+      </c>
       <c r="G68" s="10" t="inlineStr"/>
       <c r="H68" s="10" t="inlineStr"/>
       <c r="I68" s="10" t="inlineStr"/>
@@ -3286,8 +3568,12 @@
           <t>Olives</t>
         </is>
       </c>
-      <c r="E69" s="9" t="inlineStr"/>
-      <c r="F69" s="9" t="inlineStr"/>
+      <c r="E69" s="19" t="n">
+        <v>-38.05521</v>
+      </c>
+      <c r="F69" s="19" t="n">
+        <v>-57.681096</v>
+      </c>
       <c r="G69" s="9" t="inlineStr"/>
       <c r="H69" s="9" t="inlineStr"/>
       <c r="I69" s="9" t="inlineStr"/>
@@ -3319,8 +3605,12 @@
         </is>
       </c>
       <c r="D70" s="8" t="inlineStr"/>
-      <c r="E70" s="10" t="inlineStr"/>
-      <c r="F70" s="10" t="inlineStr"/>
+      <c r="E70" s="19" t="n">
+        <v>-38.05508</v>
+      </c>
+      <c r="F70" s="19" t="n">
+        <v>-57.680938</v>
+      </c>
       <c r="G70" s="10" t="inlineStr"/>
       <c r="H70" s="10" t="inlineStr"/>
       <c r="I70" s="10" t="inlineStr"/>
@@ -3356,8 +3646,12 @@
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="E71" s="9" t="inlineStr"/>
-      <c r="F71" s="9" t="inlineStr"/>
+      <c r="E71" s="19" t="n">
+        <v>-38.05502</v>
+      </c>
+      <c r="F71" s="19" t="n">
+        <v>-57.680618</v>
+      </c>
       <c r="G71" s="9" t="inlineStr"/>
       <c r="H71" s="9" t="inlineStr"/>
       <c r="I71" s="9" t="inlineStr"/>
@@ -3393,8 +3687,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E72" s="10" t="inlineStr"/>
-      <c r="F72" s="10" t="inlineStr"/>
+      <c r="E72" s="19" t="n">
+        <v>-38.05503</v>
+      </c>
+      <c r="F72" s="19" t="n">
+        <v>-57.680501</v>
+      </c>
       <c r="G72" s="10" t="inlineStr"/>
       <c r="H72" s="10" t="inlineStr"/>
       <c r="I72" s="10" t="inlineStr"/>
@@ -3430,8 +3728,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E73" s="9" t="inlineStr"/>
-      <c r="F73" s="9" t="inlineStr"/>
+      <c r="E73" s="19" t="n">
+        <v>-38.05532</v>
+      </c>
+      <c r="F73" s="19" t="n">
+        <v>-57.680429</v>
+      </c>
       <c r="G73" s="9" t="inlineStr"/>
       <c r="H73" s="9" t="inlineStr"/>
       <c r="I73" s="9" t="inlineStr"/>
@@ -3467,8 +3769,12 @@
           <t>Nothofagaceae</t>
         </is>
       </c>
-      <c r="E74" s="10" t="inlineStr"/>
-      <c r="F74" s="10" t="inlineStr"/>
+      <c r="E74" s="19" t="n">
+        <v>-38.05529</v>
+      </c>
+      <c r="F74" s="19" t="n">
+        <v>-57.680601</v>
+      </c>
       <c r="G74" s="10" t="inlineStr"/>
       <c r="H74" s="10" t="inlineStr"/>
       <c r="I74" s="10" t="inlineStr"/>
@@ -3504,8 +3810,12 @@
           <t>Nothofagaceae</t>
         </is>
       </c>
-      <c r="E75" s="9" t="inlineStr"/>
-      <c r="F75" s="9" t="inlineStr"/>
+      <c r="E75" s="19" t="n">
+        <v>-38.05553</v>
+      </c>
+      <c r="F75" s="19" t="n">
+        <v>-57.680985</v>
+      </c>
       <c r="G75" s="9" t="inlineStr"/>
       <c r="H75" s="9" t="inlineStr"/>
       <c r="I75" s="9" t="inlineStr"/>
@@ -3541,8 +3851,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E76" s="10" t="inlineStr"/>
-      <c r="F76" s="10" t="inlineStr"/>
+      <c r="E76" s="19" t="n">
+        <v>-38.05566</v>
+      </c>
+      <c r="F76" s="19" t="n">
+        <v>-57.681065</v>
+      </c>
       <c r="G76" s="10" t="inlineStr"/>
       <c r="H76" s="10" t="inlineStr"/>
       <c r="I76" s="10" t="inlineStr"/>
@@ -3574,8 +3888,12 @@
         </is>
       </c>
       <c r="D77" s="8" t="inlineStr"/>
-      <c r="E77" s="9" t="inlineStr"/>
-      <c r="F77" s="9" t="inlineStr"/>
+      <c r="E77" s="19" t="n">
+        <v>-38.05593</v>
+      </c>
+      <c r="F77" s="19" t="n">
+        <v>-57.681297</v>
+      </c>
       <c r="G77" s="9" t="inlineStr"/>
       <c r="H77" s="9" t="inlineStr"/>
       <c r="I77" s="9" t="inlineStr"/>
@@ -3611,8 +3929,12 @@
           <t>Ginkgoaceae</t>
         </is>
       </c>
-      <c r="E78" s="10" t="inlineStr"/>
-      <c r="F78" s="10" t="inlineStr"/>
+      <c r="E78" s="19" t="n">
+        <v>-38.056</v>
+      </c>
+      <c r="F78" s="19" t="n">
+        <v>-57.681529</v>
+      </c>
       <c r="G78" s="10" t="inlineStr"/>
       <c r="H78" s="10" t="inlineStr"/>
       <c r="I78" s="10" t="inlineStr"/>
@@ -3648,8 +3970,12 @@
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="E79" s="9" t="inlineStr"/>
-      <c r="F79" s="9" t="inlineStr"/>
+      <c r="E79" s="19" t="n">
+        <v>-38.05622</v>
+      </c>
+      <c r="F79" s="19" t="n">
+        <v>-57.681656</v>
+      </c>
       <c r="G79" s="9" t="inlineStr"/>
       <c r="H79" s="9" t="inlineStr"/>
       <c r="I79" s="9" t="inlineStr"/>
@@ -3685,8 +4011,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E80" s="10" t="inlineStr"/>
-      <c r="F80" s="10" t="inlineStr"/>
+      <c r="E80" s="19" t="n">
+        <v>-38.05649</v>
+      </c>
+      <c r="F80" s="19" t="n">
+        <v>-57.682174</v>
+      </c>
       <c r="G80" s="10" t="inlineStr"/>
       <c r="H80" s="10" t="inlineStr"/>
       <c r="I80" s="10" t="inlineStr"/>
@@ -3722,8 +4052,12 @@
           <t>Oleaceae</t>
         </is>
       </c>
-      <c r="E81" s="9" t="inlineStr"/>
-      <c r="F81" s="9" t="inlineStr"/>
+      <c r="E81" s="19" t="n">
+        <v>-38.05608</v>
+      </c>
+      <c r="F81" s="19" t="n">
+        <v>-57.682552</v>
+      </c>
       <c r="G81" s="9" t="inlineStr"/>
       <c r="H81" s="9" t="inlineStr"/>
       <c r="I81" s="9" t="inlineStr"/>
@@ -3759,8 +4093,12 @@
           <t>Oleaceae</t>
         </is>
       </c>
-      <c r="E82" s="10" t="inlineStr"/>
-      <c r="F82" s="10" t="inlineStr"/>
+      <c r="E82" s="19" t="n">
+        <v>-38.0561</v>
+      </c>
+      <c r="F82" s="19" t="n">
+        <v>-57.682554</v>
+      </c>
       <c r="G82" s="10" t="inlineStr"/>
       <c r="H82" s="10" t="inlineStr"/>
       <c r="I82" s="10" t="inlineStr"/>
@@ -3796,8 +4134,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E83" s="9" t="inlineStr"/>
-      <c r="F83" s="9" t="inlineStr"/>
+      <c r="E83" s="19" t="n">
+        <v>-38.05547</v>
+      </c>
+      <c r="F83" s="19" t="n">
+        <v>-57.682776</v>
+      </c>
       <c r="G83" s="9" t="inlineStr"/>
       <c r="H83" s="9" t="inlineStr"/>
       <c r="I83" s="9" t="inlineStr"/>
@@ -3829,8 +4171,12 @@
         </is>
       </c>
       <c r="D84" s="8" t="inlineStr"/>
-      <c r="E84" s="10" t="inlineStr"/>
-      <c r="F84" s="10" t="inlineStr"/>
+      <c r="E84" s="19" t="n">
+        <v>-38.05527</v>
+      </c>
+      <c r="F84" s="19" t="n">
+        <v>-57.68253</v>
+      </c>
       <c r="G84" s="10" t="inlineStr"/>
       <c r="H84" s="10" t="inlineStr"/>
       <c r="I84" s="10" t="inlineStr"/>
@@ -3866,8 +4212,12 @@
           <t>Cannabaceae</t>
         </is>
       </c>
-      <c r="E85" s="9" t="inlineStr"/>
-      <c r="F85" s="9" t="inlineStr"/>
+      <c r="E85" s="19" t="n">
+        <v>-38.05461</v>
+      </c>
+      <c r="F85" s="19" t="n">
+        <v>-57.681095</v>
+      </c>
       <c r="G85" s="9" t="inlineStr"/>
       <c r="H85" s="9" t="inlineStr"/>
       <c r="I85" s="9" t="inlineStr"/>
@@ -3903,8 +4253,12 @@
           <t>Arecaceae</t>
         </is>
       </c>
-      <c r="E86" s="10" t="inlineStr"/>
-      <c r="F86" s="10" t="inlineStr"/>
+      <c r="E86" s="19" t="n">
+        <v>-38.05491</v>
+      </c>
+      <c r="F86" s="19" t="n">
+        <v>-57.681428</v>
+      </c>
       <c r="G86" s="10" t="inlineStr"/>
       <c r="H86" s="10" t="inlineStr"/>
       <c r="I86" s="10" t="inlineStr"/>
@@ -3940,8 +4294,12 @@
           <t>Cannabaceae</t>
         </is>
       </c>
-      <c r="E87" s="9" t="inlineStr"/>
-      <c r="F87" s="9" t="inlineStr"/>
+      <c r="E87" s="19" t="n">
+        <v>-38.05494</v>
+      </c>
+      <c r="F87" s="19" t="n">
+        <v>-57.681583</v>
+      </c>
       <c r="G87" s="9" t="inlineStr"/>
       <c r="H87" s="9" t="inlineStr"/>
       <c r="I87" s="9" t="inlineStr"/>
@@ -3977,8 +4335,12 @@
           <t>Cannabaceae</t>
         </is>
       </c>
-      <c r="E88" s="10" t="inlineStr"/>
-      <c r="F88" s="10" t="inlineStr"/>
+      <c r="E88" s="19" t="n">
+        <v>-38.05503</v>
+      </c>
+      <c r="F88" s="19" t="n">
+        <v>-57.681492</v>
+      </c>
       <c r="G88" s="10" t="inlineStr"/>
       <c r="H88" s="10" t="inlineStr"/>
       <c r="I88" s="10" t="inlineStr"/>
@@ -4014,8 +4376,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E89" s="9" t="inlineStr"/>
-      <c r="F89" s="9" t="inlineStr"/>
+      <c r="E89" s="19" t="n">
+        <v>-38.05506</v>
+      </c>
+      <c r="F89" s="19" t="n">
+        <v>-57.681479</v>
+      </c>
       <c r="G89" s="9" t="inlineStr"/>
       <c r="H89" s="9" t="inlineStr"/>
       <c r="I89" s="9" t="inlineStr"/>
@@ -4051,8 +4417,12 @@
           <t>Pinaceae</t>
         </is>
       </c>
-      <c r="E90" s="10" t="inlineStr"/>
-      <c r="F90" s="10" t="inlineStr"/>
+      <c r="E90" s="19" t="n">
+        <v>-38.05528</v>
+      </c>
+      <c r="F90" s="19" t="n">
+        <v>-57.681835</v>
+      </c>
       <c r="G90" s="10" t="inlineStr"/>
       <c r="H90" s="10" t="inlineStr"/>
       <c r="I90" s="10" t="inlineStr"/>
@@ -4088,8 +4458,12 @@
           <t>Cupressaceae</t>
         </is>
       </c>
-      <c r="E91" s="9" t="inlineStr"/>
-      <c r="F91" s="9" t="inlineStr"/>
+      <c r="E91" s="19" t="n">
+        <v>-38.05525</v>
+      </c>
+      <c r="F91" s="19" t="n">
+        <v>-57.681941</v>
+      </c>
       <c r="G91" s="9" t="inlineStr"/>
       <c r="H91" s="9" t="inlineStr"/>
       <c r="I91" s="9" t="inlineStr"/>
@@ -4125,8 +4499,12 @@
           <t>Fagaceae</t>
         </is>
       </c>
-      <c r="E92" s="10" t="inlineStr"/>
-      <c r="F92" s="10" t="inlineStr"/>
+      <c r="E92" s="19" t="n">
+        <v>-38.05504</v>
+      </c>
+      <c r="F92" s="19" t="n">
+        <v>-57.680912</v>
+      </c>
       <c r="G92" s="10" t="inlineStr"/>
       <c r="H92" s="10" t="inlineStr"/>
       <c r="I92" s="10" t="inlineStr"/>
@@ -4158,8 +4536,12 @@
         </is>
       </c>
       <c r="D93" s="8" t="inlineStr"/>
-      <c r="E93" s="9" t="inlineStr"/>
-      <c r="F93" s="9" t="inlineStr"/>
+      <c r="E93" s="19" t="n">
+        <v>-38.0551</v>
+      </c>
+      <c r="F93" s="19" t="n">
+        <v>-57.680595</v>
+      </c>
       <c r="G93" s="9" t="inlineStr"/>
       <c r="H93" s="9" t="inlineStr"/>
       <c r="I93" s="9" t="inlineStr"/>
